--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_BUENO ARENAS ALBACETE BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_BUENO ARENAS ALBACETE BASKET.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>373.36</v>
+        <v>449.68</v>
       </c>
       <c r="C2" t="n">
-        <v>373.0600000000001</v>
+        <v>449.52</v>
       </c>
       <c r="D2" t="n">
-        <v>104.8088779284833</v>
+        <v>102.1089161772557</v>
       </c>
       <c r="E2" t="n">
-        <v>93.28258189031254</v>
+        <v>92.09823812066203</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.4811320754716981</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1320972235565376</v>
+        <v>0.1350063532401525</v>
       </c>
       <c r="H2" t="n">
-        <v>0.225130890052356</v>
+        <v>0.2327586206896552</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2653721682847897</v>
+        <v>0.2749326145552561</v>
       </c>
       <c r="J2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="M2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N2" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="O2" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4530744336569579</v>
+        <v>0.4528301886792453</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05825242718446602</v>
+        <v>0.05390835579514825</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
+        <v>17</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.04582210242587601</v>
+      </c>
+      <c r="W2" t="n">
         <v>12</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.03883495145631068</v>
-      </c>
-      <c r="W2" t="n">
-        <v>10</v>
-      </c>
       <c r="X2" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1326860841423948</v>
+        <v>0.1347708894878706</v>
       </c>
       <c r="Z2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AA2" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3171521035598706</v>
+        <v>0.3126684636118598</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.25</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.24</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3362068965517241</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.142857142857143</v>
+        <v>1.107142857142857</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9712230215827338</v>
+        <v>0.9216867469879518</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4461538461538462</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.837209302325581</v>
+        <v>1.696428571428571</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.545454545454545</v>
+        <v>1.367647058823529</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.618181818181818</v>
+        <v>5.455882352941177</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.163636363636364</v>
+        <v>6.823529411764706</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.672</v>
+        <v>74.94666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>74.61200000000001</v>
+        <v>74.92</v>
       </c>
       <c r="D3" t="n">
-        <v>104.8088779284833</v>
+        <v>102.1089161772557</v>
       </c>
       <c r="E3" t="n">
-        <v>93.28258189031253</v>
+        <v>92.09823812066203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.4811320754716982</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1320972235565376</v>
+        <v>0.1350063532401525</v>
       </c>
       <c r="H3" t="n">
-        <v>0.225130890052356</v>
+        <v>0.2327586206896551</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2653721682847897</v>
+        <v>0.2749326145552561</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>15.8</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="O3" t="n">
         <v>28</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4530744336569579</v>
+        <v>0.4528301886792453</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05825242718446602</v>
+        <v>0.05390835579514826</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03883495145631068</v>
+        <v>0.04582210242587602</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1326860841423948</v>
+        <v>0.1347708894878706</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.6</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3171521035598706</v>
+        <v>0.3126684636118598</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.25</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2439024390243903</v>
+        <v>0.24</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3571428571428571</v>
+        <v>0.3362068965517241</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.142857142857143</v>
+        <v>1.107142857142857</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.5</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9712230215827338</v>
+        <v>0.9216867469879518</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.4461538461538461</v>
+        <v>0.3974358974358975</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3703703703703704</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.837209302325582</v>
+        <v>1.696428571428571</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.545454545454545</v>
+        <v>1.367647058823529</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.618181818181818</v>
+        <v>5.455882352941176</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.163636363636363</v>
+        <v>6.823529411764705</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>372.76</v>
+        <v>449.36</v>
       </c>
       <c r="C4" t="n">
-        <v>373.0600000000001</v>
+        <v>449.52</v>
       </c>
       <c r="D4" t="n">
-        <v>93.28258189031254</v>
+        <v>92.09823812066203</v>
       </c>
       <c r="E4" t="n">
-        <v>104.8088779284833</v>
+        <v>102.1089161772557</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4040697674418605</v>
+        <v>0.4070048309178744</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1429325358430821</v>
+        <v>0.1432875303108237</v>
       </c>
       <c r="H4" t="n">
-        <v>0.351931330472103</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2034883720930233</v>
+        <v>0.1859903381642512</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L4" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="M4" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="O4" t="n">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4244186046511628</v>
+        <v>0.4227053140096618</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04941860465116279</v>
+        <v>0.04589371980676329</v>
       </c>
       <c r="T4" t="n">
         <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07267441860465117</v>
+        <v>0.06280193236714976</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X4" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1540697674418605</v>
+        <v>0.1618357487922705</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AA4" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2965116279069768</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4685714285714286</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.36</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2549019607843137</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.9041095890410958</v>
+        <v>0.9371428571428572</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.72</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.7354838709677419</v>
+        <v>0.7305699481865285</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.4181818181818182</v>
+        <v>0.4558823529411765</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.6631578947368421</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.928571428571429</v>
+        <v>2.03030303030303</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.292307692307692</v>
+        <v>5.307692307692307</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>6.282051282051282</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.55200000000001</v>
+        <v>74.89333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>74.61200000000001</v>
+        <v>74.92</v>
       </c>
       <c r="D5" t="n">
-        <v>93.28258189031253</v>
+        <v>92.09823812066203</v>
       </c>
       <c r="E5" t="n">
-        <v>104.8088779284833</v>
+        <v>102.1089161772557</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4040697674418605</v>
+        <v>0.4070048309178744</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1429325358430821</v>
+        <v>0.1432875303108237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.351931330472103</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2034883720930233</v>
+        <v>0.1859903381642512</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="L5" t="n">
-        <v>10.8</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>13.2</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>29.2</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4244186046511628</v>
+        <v>0.4227053140096618</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04941860465116279</v>
+        <v>0.04589371980676328</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07267441860465117</v>
+        <v>0.06280193236714976</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>10.6</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1540697674418605</v>
+        <v>0.1618357487922705</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2965116279069767</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4685714285714285</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.36</v>
+        <v>0.3461538461538462</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2549019607843138</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.9041095890410958</v>
+        <v>0.9371428571428571</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.72</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.7354838709677418</v>
+        <v>0.7305699481865285</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.4181818181818182</v>
+        <v>0.4558823529411765</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.7073170731707318</v>
+        <v>0.6631578947368421</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.928571428571429</v>
+        <v>2.03030303030303</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9076923076923078</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.292307692307692</v>
+        <v>5.307692307692307</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.199999999999999</v>
+        <v>6.282051282051283</v>
       </c>
     </row>
     <row r="7">
@@ -1429,22 +1429,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -1453,10 +1453,10 @@
         <v>9</v>
       </c>
       <c r="J8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" t="n">
         <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1471,19 +1471,19 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
@@ -1492,19 +1492,19 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
+        <v>12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" t="n">
         <v>10</v>
       </c>
-      <c r="X8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8</v>
-      </c>
       <c r="AA8" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -1544,47 +1544,47 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>63:41</t>
+          <t>76:20</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>30.96</v>
+        <v>34.96</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.457</v>
+        <v>0.442</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.501</v>
+        <v>0.484</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.872</v>
+        <v>0.83</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.129</v>
+        <v>0.143</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.261</v>
+        <v>0.231</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.234</v>
+        <v>0.218</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.054</v>
+        <v>0.067</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.049</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="9">
@@ -1594,37 +1594,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" t="n">
         <v>18</v>
       </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>21</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>19</v>
-      </c>
-      <c r="K9" t="n">
-        <v>16</v>
-      </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
         <v>8</v>
@@ -1636,19 +1636,19 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U9" t="n">
         <v>6</v>
@@ -1657,19 +1657,19 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5</v>
+        <v>0.474</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
@@ -1699,57 +1699,57 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.389</v>
+        <v>0.381</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>125:40</t>
+          <t>143:19</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>50.08</v>
+        <v>60.84</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.499</v>
+        <v>0.502</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.839</v>
+        <v>0.822</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.16</v>
+        <v>0.181</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.077</v>
+        <v>0.133</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.375</v>
+        <v>1.818</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.875</v>
+        <v>4.091</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.25</v>
+        <v>5.909</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.164</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="10">
@@ -1759,61 +1759,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U10" t="n">
         <v>3</v>
@@ -1822,99 +1822,99 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AH10" t="n">
         <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>182:31</t>
+        </is>
+      </c>
+      <c r="AO10" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AP10" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>147:12</t>
-        </is>
-      </c>
-      <c r="AO10" t="n">
-        <v>60.12</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.5679999999999999</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>0.637</v>
+        <v>0.587</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.148</v>
+        <v>1.064</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.1</v>
+        <v>0.093</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.432</v>
+        <v>0.455</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.833</v>
+        <v>0.714</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.333</v>
+        <v>7.857</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.167</v>
+        <v>8.571</v>
       </c>
       <c r="AX10" t="n">
         <v>0.196</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.128</v>
+        <v>0.117</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.045</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="11">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
@@ -2070,7 +2070,7 @@
         <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.242</v>
+        <v>0.24</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="12">
@@ -2089,37 +2089,37 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>55</v>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
-        <v>45</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
         <v>6</v>
@@ -2131,40 +2131,40 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
+        <v>17</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>102</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>13</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>94</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>9</v>
       </c>
-      <c r="X12" t="n">
-        <v>6</v>
-      </c>
       <c r="Y12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2</v>
+        <v>0.278</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2188,63 +2188,63 @@
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>140:50</t>
+          <t>172:46</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>54.92</v>
+        <v>67.56</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.423</v>
+        <v>0.417</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.819</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.146</v>
+        <v>0.133</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.75</v>
+        <v>4.333</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.875</v>
+        <v>5.333</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.625</v>
+        <v>9.667</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.311</v>
+        <v>0.303</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.317</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="13">
@@ -2254,46 +2254,46 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
         <v>6</v>
@@ -2302,40 +2302,40 @@
         <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.462</v>
+        <v>0.467</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2353,63 +2353,63 @@
         <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.4</v>
+        <v>0.286</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.091</v>
+        <v>0.167</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>82:17</t>
+          <t>95:33</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>41.52</v>
+        <v>49.72</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.328</v>
+        <v>0.342</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.366</v>
+        <v>0.412</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.626</v>
+        <v>0.724</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.145</v>
+        <v>0.121</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.156</v>
+        <v>0.263</v>
       </c>
       <c r="AU13" t="n">
         <v>0.667</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.333</v>
+        <v>6.333</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.242</v>
+        <v>0.248</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="14">
@@ -2419,64 +2419,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" t="n">
         <v>12</v>
       </c>
-      <c r="H14" t="n">
-        <v>10</v>
-      </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V14" t="n">
         <v>2</v>
@@ -2488,13 +2488,13 @@
         <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2506,75 +2506,75 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>104:31</t>
+          <t>130:21</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>36.28</v>
+        <v>44.16</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.45</v>
+        <v>0.472</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.524</v>
+        <v>0.546</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.02</v>
+        <v>1.042</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.028</v>
+        <v>0.045</v>
       </c>
       <c r="AT14" t="n">
         <v>0.333</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.025</v>
+        <v>0.039</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="15">
@@ -2584,22 +2584,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15" t="n">
         <v>2</v>
@@ -2653,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.75</v>
+        <v>0.778</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2683,10 +2683,10 @@
         <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2699,23 +2699,23 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47:40</t>
+          <t>51:03</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>20.44</v>
+        <v>22.44</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.577</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.734</v>
+        <v>0.758</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.342</v>
+        <v>0.312</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
@@ -2724,22 +2724,22 @@
         <v>0.286</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.857</v>
+        <v>2.143</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.143</v>
+        <v>2.429</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.066</v>
+        <v>0.061</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="16">
@@ -2749,16 +2749,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2767,19 +2767,19 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
         <v>8</v>
@@ -2803,28 +2803,28 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.654</v>
+        <v>0.677</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -2864,47 +2864,47 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>79:53</t>
+          <t>97:18</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>42.6</v>
+        <v>50.48</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.613</v>
+        <v>0.639</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.638</v>
+        <v>0.655</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.127</v>
+        <v>1.129</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.117</v>
+        <v>0.139</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.323</v>
+        <v>0.306</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.2</v>
+        <v>5.143</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>5.286</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.256</v>
+        <v>0.247</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.123</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="17">
@@ -2914,22 +2914,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H17" t="n">
         <v>9</v>
@@ -2938,13 +2938,13 @@
         <v>12</v>
       </c>
       <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>14</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3</v>
       </c>
       <c r="M17" t="n">
         <v>2</v>
@@ -2956,19 +2956,19 @@
         <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="U17" t="n">
         <v>2</v>
@@ -2983,13 +2983,13 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.714</v>
+        <v>0.6</v>
       </c>
       <c r="AB17" t="n">
         <v>2</v>
@@ -3022,54 +3022,54 @@
         <v>6</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.462</v>
+        <v>0.375</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>109:45</t>
+          <t>128:04</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>36.28</v>
+        <v>45.28</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.661</v>
+        <v>0.574</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.268</v>
+        <v>1.06</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.321</v>
+        <v>0.265</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.333</v>
+        <v>0.833</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.333</v>
+        <v>5.667</v>
       </c>
       <c r="AW17" t="n">
-        <v>10.667</v>
+        <v>6.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.159</v>
+        <v>0.168</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="18">
@@ -3079,46 +3079,46 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
         <v>14</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>12</v>
       </c>
       <c r="H18" t="n">
         <v>6</v>
       </c>
       <c r="I18" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
         <v>12</v>
       </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>11</v>
-      </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
         <v>15</v>
@@ -3148,13 +3148,13 @@
         <v>7</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.846</v>
+        <v>0.667</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3169,72 +3169,72 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
         <v>2</v>
       </c>
-      <c r="AI18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1</v>
-      </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>86:50</t>
+          <t>111:04</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>32.28</v>
+        <v>41.16</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.538</v>
+        <v>0.485</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.543</v>
+        <v>0.486</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.053</v>
+        <v>0.948</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.231</v>
+        <v>0.176</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.179</v>
+        <v>0.177</v>
       </c>
       <c r="AY18" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.109</v>
+        <v>0.093</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="19">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -3286,10 +3286,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -3409,159 +3409,159 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>391</v>
+        <v>459</v>
       </c>
       <c r="D20" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E20" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G20" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="H20" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I20" t="n">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="J20" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K20" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P20" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="R20" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="U20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="W20" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="X20" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="Y20" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="Z20" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.571</v>
+        <v>0.554</v>
       </c>
       <c r="AB20" t="n">
         <v>4</v>
       </c>
       <c r="AC20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AH20" t="n">
         <v>12</v>
       </c>
-      <c r="AG20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>10</v>
-      </c>
       <c r="AI20" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.244</v>
+        <v>0.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AL20" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.357</v>
+        <v>0.336</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>416.36</v>
+        <v>503.68</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.541</v>
+        <v>0.527</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.911</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.265</v>
+        <v>0.275</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.545</v>
+        <v>1.368</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.618</v>
+        <v>5.456</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.164</v>
+        <v>6.824</v>
       </c>
       <c r="AX20" t="n">
         <v>0.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -3574,159 +3574,159 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>348</v>
+        <v>414</v>
       </c>
       <c r="D21" t="n">
+        <v>98</v>
+      </c>
+      <c r="E21" t="n">
+        <v>221</v>
+      </c>
+      <c r="F21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G21" t="n">
+        <v>193</v>
+      </c>
+      <c r="H21" t="n">
+        <v>77</v>
+      </c>
+      <c r="I21" t="n">
+        <v>119</v>
+      </c>
+      <c r="J21" t="n">
+        <v>76</v>
+      </c>
+      <c r="K21" t="n">
+        <v>178</v>
+      </c>
+      <c r="L21" t="n">
+        <v>95</v>
+      </c>
+      <c r="M21" t="n">
+        <v>32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13</v>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>40</v>
+      </c>
+      <c r="R21" t="n">
+        <v>135</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>253</v>
+      </c>
+      <c r="U21" t="n">
+        <v>31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>63</v>
+      </c>
+      <c r="W21" t="n">
+        <v>67</v>
+      </c>
+      <c r="X21" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y21" t="n">
         <v>82</v>
       </c>
-      <c r="E21" t="n">
-        <v>189</v>
-      </c>
-      <c r="F21" t="n">
-        <v>38</v>
-      </c>
-      <c r="G21" t="n">
-        <v>155</v>
-      </c>
-      <c r="H21" t="n">
-        <v>70</v>
-      </c>
-      <c r="I21" t="n">
-        <v>104</v>
-      </c>
-      <c r="J21" t="n">
-        <v>59</v>
-      </c>
-      <c r="K21" t="n">
-        <v>148</v>
-      </c>
-      <c r="L21" t="n">
-        <v>82</v>
-      </c>
-      <c r="M21" t="n">
-        <v>26</v>
-      </c>
-      <c r="N21" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" t="n">
-        <v>7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>31</v>
-      </c>
-      <c r="R21" t="n">
-        <v>109</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>216</v>
-      </c>
-      <c r="U21" t="n">
-        <v>23</v>
-      </c>
-      <c r="V21" t="n">
-        <v>58</v>
-      </c>
-      <c r="W21" t="n">
-        <v>54</v>
-      </c>
-      <c r="X21" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>66</v>
-      </c>
       <c r="Z21" t="n">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.452</v>
+        <v>0.469</v>
       </c>
       <c r="AB21" t="n">
         <v>6</v>
       </c>
       <c r="AC21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.353</v>
+        <v>0.316</v>
       </c>
       <c r="AE21" t="n">
         <v>9</v>
       </c>
       <c r="AF21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.36</v>
+        <v>0.346</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.226</v>
+        <v>0.209</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AL21" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.255</v>
+        <v>0.262</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>454.76</v>
+        <v>544.36</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.404</v>
+        <v>0.407</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.765</v>
+        <v>0.761</v>
       </c>
       <c r="AS21" t="n">
         <v>0.143</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.203</v>
+        <v>0.186</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.908</v>
+        <v>0.974</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.292</v>
+        <v>5.308</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.2</v>
+        <v>6.282</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.155</v>
+        <v>0.153</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3798,40 +3798,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>5.4</v>
+        <v>4.833</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3840,22 +3840,22 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3867,19 +3867,19 @@
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -3897,63 +3897,63 @@
         <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="AM23" t="n">
         <v>0.375</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>6.192</v>
+        <v>5.827</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.457</v>
+        <v>0.442</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.501</v>
+        <v>0.484</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.872</v>
+        <v>0.83</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.129</v>
+        <v>0.143</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.261</v>
+        <v>0.231</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.234</v>
+        <v>0.218</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.054</v>
+        <v>0.067</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.049</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="24">
@@ -3963,40 +3963,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>8.4</v>
+        <v>8.333</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="E24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="G24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.833</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.333</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -4005,46 +4005,46 @@
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6</v>
+        <v>1.833</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>35</v>
+      </c>
+      <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>34</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.2</v>
-      </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>3.167</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5</v>
+        <v>0.474</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AD24" t="n">
         <v>0.5</v>
@@ -4062,63 +4062,63 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AL24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.389</v>
+        <v>0.381</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>25:08</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>10.016</v>
+        <v>10.14</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.499</v>
+        <v>0.502</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.839</v>
+        <v>0.822</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.16</v>
+        <v>0.181</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.077</v>
+        <v>0.133</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.375</v>
+        <v>1.818</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.875</v>
+        <v>4.091</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.25</v>
+        <v>5.909</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.164</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="25">
@@ -4128,162 +4128,162 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>13.333</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="C25" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J25" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.8</v>
-      </c>
       <c r="M25" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="R25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.4</v>
+        <v>2.667</v>
       </c>
       <c r="X25" t="n">
-        <v>1.2</v>
+        <v>1.667</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.6</v>
+        <v>3.333</v>
       </c>
       <c r="AA25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>30:25</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>12.533</v>
+      </c>
+      <c r="AP25" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>29:26</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>12.024</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.5679999999999999</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>0.637</v>
+        <v>0.587</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.148</v>
+        <v>1.064</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.1</v>
+        <v>0.093</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.432</v>
+        <v>0.455</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.833</v>
+        <v>0.714</v>
       </c>
       <c r="AV25" t="n">
-        <v>7.333</v>
+        <v>7.857</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.167</v>
+        <v>8.571</v>
       </c>
       <c r="AX25" t="n">
         <v>0.196</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.128</v>
+        <v>0.117</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.045</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="26">
@@ -4293,31 +4293,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -4335,13 +4335,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4401,18 +4401,18 @@
         <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>02:20</t>
+          <t>01:56</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>1.176</v>
+        <v>0.98</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.242</v>
+        <v>0.24</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="27">
@@ -4458,61 +4458,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>9.167</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="E27" t="n">
-        <v>3.4</v>
+        <v>3.333</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="G27" t="n">
-        <v>4.4</v>
+        <v>4.667</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="K27" t="n">
-        <v>10.2</v>
+        <v>10.167</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="R27" t="n">
-        <v>2.6</v>
+        <v>2.833</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -4521,25 +4521,25 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8</v>
+        <v>2.167</v>
       </c>
       <c r="X27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="Z27" t="n">
         <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.2</v>
+        <v>0.278</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4554,66 +4554,66 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>4</v>
+        <v>4.167</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>28:10</t>
+          <t>28:47</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>10.984</v>
+        <v>11.26</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.423</v>
+        <v>0.417</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.819</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.146</v>
+        <v>0.133</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.75</v>
+        <v>4.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.875</v>
+        <v>5.333</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.625</v>
+        <v>9.667</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.311</v>
+        <v>0.303</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.317</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="28">
@@ -4623,34 +4623,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>3.167</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G28" t="n">
-        <v>3.2</v>
+        <v>3.167</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>2.167</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="K28" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -4659,16 +4659,16 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="R28" t="n">
         <v>2</v>
@@ -4677,108 +4677,108 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AL28" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AM28" t="n">
-        <v>0.091</v>
+        <v>0.167</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>8.304</v>
+        <v>8.287000000000001</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.328</v>
+        <v>0.342</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.366</v>
+        <v>0.412</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.626</v>
+        <v>0.724</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.145</v>
+        <v>0.121</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.156</v>
+        <v>0.263</v>
       </c>
       <c r="AU28" t="n">
         <v>0.667</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.333</v>
+        <v>6.333</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.242</v>
+        <v>0.248</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.094</v>
+        <v>0.099</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="29">
@@ -4788,82 +4788,82 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>7.4</v>
+        <v>7.667</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="E29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>21</v>
+      </c>
+      <c r="U29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>13</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.8</v>
-      </c>
       <c r="V29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="X29" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4875,75 +4875,75 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>7.256</v>
+        <v>7.36</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.45</v>
+        <v>0.472</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.524</v>
+        <v>0.546</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.02</v>
+        <v>1.042</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.028</v>
+        <v>0.045</v>
       </c>
       <c r="AT29" t="n">
         <v>0.333</v>
       </c>
       <c r="AU29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV29" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AW29" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.025</v>
+        <v>0.039</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="30">
@@ -4953,67 +4953,67 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -5022,19 +5022,19 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.75</v>
+        <v>0.778</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -5049,42 +5049,42 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>4.088</v>
+        <v>3.74</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.577</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.734</v>
+        <v>0.758</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.342</v>
+        <v>0.312</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
@@ -5093,22 +5093,22 @@
         <v>0.286</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.857</v>
+        <v>2.143</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.143</v>
+        <v>2.429</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.066</v>
+        <v>0.061</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="31">
@@ -5118,16 +5118,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="D31" t="n">
-        <v>3.8</v>
+        <v>3.833</v>
       </c>
       <c r="E31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -5136,79 +5136,79 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="K31" t="n">
-        <v>2.6</v>
+        <v>2.333</v>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="R31" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="W31" t="n">
-        <v>2.8</v>
+        <v>2.667</v>
       </c>
       <c r="X31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.2</v>
+        <v>5.167</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.654</v>
+        <v>0.677</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AD31" t="n">
         <v>0.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AG31" t="n">
         <v>0.333</v>
@@ -5233,47 +5233,47 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>8.52</v>
+        <v>8.413</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.613</v>
+        <v>0.639</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.638</v>
+        <v>0.655</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.127</v>
+        <v>1.129</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.117</v>
+        <v>0.139</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.323</v>
+        <v>0.306</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.2</v>
+        <v>5.143</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>5.286</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.256</v>
+        <v>0.247</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.14</v>
+        <v>0.123</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="32">
@@ -5283,162 +5283,162 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>3.167</v>
       </c>
       <c r="H32" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="K32" t="n">
-        <v>2.8</v>
+        <v>2.667</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O32" t="n">
         <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="R32" t="n">
-        <v>1.6</v>
+        <v>1.833</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="X32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Y32" t="n">
         <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.714</v>
+        <v>0.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AD32" t="n">
         <v>0.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AG32" t="n">
         <v>1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.333</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.6</v>
+        <v>2.667</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.462</v>
+        <v>0.375</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>7.256</v>
+        <v>7.547</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.661</v>
+        <v>0.574</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.268</v>
+        <v>1.06</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.321</v>
+        <v>0.265</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.333</v>
+        <v>0.833</v>
       </c>
       <c r="AV32" t="n">
-        <v>9.333</v>
+        <v>5.667</v>
       </c>
       <c r="AW32" t="n">
-        <v>10.667</v>
+        <v>6.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.159</v>
+        <v>0.168</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="33">
@@ -5448,55 +5448,55 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.8</v>
+        <v>3.333</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K33" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5505,31 +5505,31 @@
         <v>26</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="W33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z33" t="n">
         <v>3</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AA33" t="n">
-        <v>0.846</v>
+        <v>0.667</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5538,72 +5538,72 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.182</v>
+        <v>0.25</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AM33" t="n">
         <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.456</v>
+        <v>6.86</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.538</v>
+        <v>0.485</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.543</v>
+        <v>0.486</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.053</v>
+        <v>0.948</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.231</v>
+        <v>0.176</v>
       </c>
       <c r="AU33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV33" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AW33" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.179</v>
+        <v>0.177</v>
       </c>
       <c r="AY33" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.109</v>
+        <v>0.093</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="34">
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1.2</v>
+        <v>2.333</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5778,118 +5778,118 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>78.2</v>
+        <v>76.5</v>
       </c>
       <c r="D35" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
-        <v>34</v>
+        <v>34.167</v>
       </c>
       <c r="F35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>27.667</v>
+      </c>
+      <c r="H35" t="n">
+        <v>17</v>
+      </c>
+      <c r="I35" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>30.833</v>
+      </c>
+      <c r="L35" t="n">
         <v>9</v>
       </c>
-      <c r="G35" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="H35" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="J35" t="n">
-        <v>17</v>
-      </c>
-      <c r="K35" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="L35" t="n">
-        <v>8.6</v>
-      </c>
       <c r="M35" t="n">
-        <v>6.8</v>
+        <v>6.333</v>
       </c>
       <c r="N35" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="O35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>11.333</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>21.4</v>
+        <v>21.167</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="U35" t="n">
-        <v>5.8</v>
+        <v>5.167</v>
       </c>
       <c r="V35" t="n">
-        <v>2.8</v>
+        <v>3.333</v>
       </c>
       <c r="W35" t="n">
-        <v>15.8</v>
+        <v>15.833</v>
       </c>
       <c r="X35" t="n">
-        <v>8.6</v>
+        <v>9.333</v>
       </c>
       <c r="Y35" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z35" t="n">
         <v>28</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.571</v>
+        <v>0.554</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.6</v>
+        <v>3.333</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.4</v>
+        <v>2.833</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="AH35" t="n">
         <v>2</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.333</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.244</v>
+        <v>0.24</v>
       </c>
       <c r="AK35" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AL35" t="n">
-        <v>19.6</v>
+        <v>19.333</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.357</v>
+        <v>0.336</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -5897,40 +5897,40 @@
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>83.27200000000001</v>
+        <v>83.947</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.541</v>
+        <v>0.527</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.911</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.265</v>
+        <v>0.275</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.545</v>
+        <v>1.368</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.618</v>
+        <v>5.456</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.164</v>
+        <v>6.824</v>
       </c>
       <c r="AX35" t="n">
         <v>0.2</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="BA35" t="n">
         <v>0</v>
@@ -5943,118 +5943,118 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>69.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="D36" t="n">
-        <v>16.4</v>
+        <v>16.333</v>
       </c>
       <c r="E36" t="n">
-        <v>37.8</v>
+        <v>36.833</v>
       </c>
       <c r="F36" t="n">
-        <v>7.6</v>
+        <v>7.833</v>
       </c>
       <c r="G36" t="n">
-        <v>31</v>
+        <v>32.167</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>12.833</v>
       </c>
       <c r="I36" t="n">
-        <v>20.8</v>
+        <v>19.833</v>
       </c>
       <c r="J36" t="n">
-        <v>11.8</v>
+        <v>12.667</v>
       </c>
       <c r="K36" t="n">
-        <v>29.6</v>
+        <v>29.667</v>
       </c>
       <c r="L36" t="n">
-        <v>16.4</v>
+        <v>15.833</v>
       </c>
       <c r="M36" t="n">
-        <v>5.2</v>
+        <v>5.333</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>2.167</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P36" t="n">
         <v>13</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.2</v>
+        <v>6.667</v>
       </c>
       <c r="R36" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="U36" t="n">
-        <v>4.6</v>
+        <v>5.167</v>
       </c>
       <c r="V36" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="W36" t="n">
-        <v>10.8</v>
+        <v>11.167</v>
       </c>
       <c r="X36" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>13.2</v>
+        <v>13.667</v>
       </c>
       <c r="Z36" t="n">
-        <v>29.2</v>
+        <v>29.167</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.452</v>
+        <v>0.469</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.4</v>
+        <v>3.167</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.353</v>
+        <v>0.316</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>5</v>
+        <v>4.333</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.36</v>
+        <v>0.346</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="AI36" t="n">
-        <v>10.6</v>
+        <v>11.167</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.226</v>
+        <v>0.209</v>
       </c>
       <c r="AK36" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.255</v>
+        <v>0.262</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
@@ -6062,37 +6062,37 @@
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>90.952</v>
+        <v>90.727</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.404</v>
+        <v>0.407</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.765</v>
+        <v>0.761</v>
       </c>
       <c r="AS36" t="n">
         <v>0.143</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.203</v>
+        <v>0.186</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.908</v>
+        <v>0.974</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.292</v>
+        <v>5.308</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.2</v>
+        <v>6.282</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.218</v>
+        <v>0.216</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="AZ36" t="n">
         <v>0.127</v>
